--- a/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
@@ -6994,6 +6994,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L142" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8310,5 +8313,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M90" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="164">
   <si>
     <r>
       <rPr>
@@ -6038,7 +6038,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6173,6 +6173,18 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -6718,13 +6730,13 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>51</v>
+      <c r="A68" s="34">
+        <v>4</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="28" t="s">
-        <v>52</v>
+      <c r="A69" s="35">
+        <v>2</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7043,14 +7055,14 @@
       <c r="B4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>92</v>
+      <c r="C4" s="36">
+        <v>3</v>
+      </c>
+      <c r="D4" s="36">
+        <v>4</v>
+      </c>
+      <c r="E4" s="36">
+        <v>5</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>93</v>
@@ -7501,14 +7513,14 @@
       <c r="B31" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>127</v>
+      <c r="C31" s="36">
+        <v>5</v>
+      </c>
+      <c r="D31" s="36">
+        <v>4</v>
+      </c>
+      <c r="E31" s="36">
+        <v>3</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>128</v>

--- a/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
+++ b/从零开始学Slots/从零开始学Slots-39-数值篇-MysterySymbols.xlsx
@@ -5850,11 +5850,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="0.0000%"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6038,7 +6039,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6185,6 +6186,22 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -7488,7 +7505,7 @@
       <c r="E28" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="38" t="n">
         <f aca="false">SUM(B28:E28)</f>
         <v>1</v>
       </c>
@@ -7548,11 +7565,11 @@
         <f aca="false">(B14+B18)*(C14+C18)*(D14+D18)*(E24-(E14+E18))*$B$24</f>
         <v>28687500</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C32/PRODUCT($B$24:$F$24))*100+(D32/PRODUCT($B$24:$F$24))*25+(E32/PRODUCT($B$24:$F$24))*5)</f>
         <v>0.0326953125</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="38" t="n">
         <f aca="false">$B$28</f>
         <v>0.25</v>
       </c>
@@ -7576,11 +7593,11 @@
         <f aca="false">(B15+B18)*(C15+C18)*(D15+D18)*(E24-(E15+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C33/PRODUCT($B$24:$F$24))*50+(D33/PRODUCT($B$24:$F$24))*13+(E33/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1220703125</v>
       </c>
-      <c r="G33" s="22" t="n">
+      <c r="G33" s="38" t="n">
         <f aca="false">$B$28</f>
         <v>0.25</v>
       </c>
@@ -7604,11 +7621,11 @@
         <f aca="false">(B16+B18)*(C16+C18)*(D16+D18)*(E24-(E16+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C34/PRODUCT($B$24:$F$24))*38+(D34/PRODUCT($B$24:$F$24))*10+(E34/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1015625</v>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="38" t="n">
         <f aca="false">$B$28</f>
         <v>0.25</v>
       </c>
@@ -7632,11 +7649,11 @@
         <f aca="false">(B17+B18+B19)*(C17+C18+C19)*(D17+D18+D19)*(E24-(E17+E18+E19))*$B$24</f>
         <v>625000000</v>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C35/PRODUCT($B$24:$F$24))*25+(D35/PRODUCT($B$24:$F$24))*8+(E35/PRODUCT($B$24:$F$24))*3)</f>
         <v>1.21875</v>
       </c>
-      <c r="G35" s="22" t="n">
+      <c r="G35" s="38" t="n">
         <f aca="false">$B$28</f>
         <v>0.25</v>
       </c>
@@ -7660,11 +7677,11 @@
         <f aca="false">(B14+B18)*(C14+C18)*(D14+D18)*(E24-(E14+E18))*$B$24</f>
         <v>28687500</v>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C36/PRODUCT($B$24:$F$24))*100+(D36/PRODUCT($B$24:$F$24))*25+(E36/PRODUCT($B$24:$F$24))*5)</f>
         <v>0.0326953125</v>
       </c>
-      <c r="G36" s="22" t="n">
+      <c r="G36" s="38" t="n">
         <f aca="false">$C$28</f>
         <v>0.25</v>
       </c>
@@ -7688,11 +7705,11 @@
         <f aca="false">(B15+B18)*(C15+C18)*(D15+D18)*(E24-(E15+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C37/PRODUCT($B$24:$F$24))*50+(D37/PRODUCT($B$24:$F$24))*13+(E37/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1220703125</v>
       </c>
-      <c r="G37" s="22" t="n">
+      <c r="G37" s="38" t="n">
         <f aca="false">$C$28</f>
         <v>0.25</v>
       </c>
@@ -7716,11 +7733,11 @@
         <f aca="false">(B16+B18+B19)*(C16+C18+C19)*(D16+D18+D19)*(E24-(E16+E18+E19))*$B$24</f>
         <v>625000000</v>
       </c>
-      <c r="F38" s="24" t="n">
+      <c r="F38" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C38/PRODUCT($B$24:$F$24))*38+(D38/PRODUCT($B$24:$F$24))*10+(E38/PRODUCT($B$24:$F$24))*3)</f>
         <v>1.6875</v>
       </c>
-      <c r="G38" s="22" t="n">
+      <c r="G38" s="38" t="n">
         <f aca="false">$C$28</f>
         <v>0.25</v>
       </c>
@@ -7744,11 +7761,11 @@
         <f aca="false">(B17+B18)*(C17+C18)*(D17+D18)*(E24-(E17+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F39" s="24" t="n">
+      <c r="F39" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C39/PRODUCT($B$24:$F$24))*25+(D39/PRODUCT($B$24:$F$24))*8+(E39/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.0830078125</v>
       </c>
-      <c r="G39" s="22" t="n">
+      <c r="G39" s="38" t="n">
         <f aca="false">$C$28</f>
         <v>0.25</v>
       </c>
@@ -7772,11 +7789,11 @@
         <f aca="false">(B14+B18)*(C14+C18)*(D14+D18)*(E24-(E14+E18))*$B$24</f>
         <v>28687500</v>
       </c>
-      <c r="F40" s="24" t="n">
+      <c r="F40" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C40/PRODUCT($B$24:$F$24))*100+(D40/PRODUCT($B$24:$F$24))*25+(E40/PRODUCT($B$24:$F$24))*5)</f>
         <v>0.0326953125</v>
       </c>
-      <c r="G40" s="22" t="n">
+      <c r="G40" s="38" t="n">
         <f aca="false">$D$28</f>
         <v>0.25</v>
       </c>
@@ -7800,11 +7817,11 @@
         <f aca="false">(B15+B18+B19)*(C15+C18+C19)*(D15+D18+D19)*(E24-(E15+E18+E19))*$B$24</f>
         <v>625000000</v>
       </c>
-      <c r="F41" s="24" t="n">
+      <c r="F41" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C41/PRODUCT($B$24:$F$24))*50+(D41/PRODUCT($B$24:$F$24))*13+(E41/PRODUCT($B$24:$F$24))*3)</f>
         <v>2.15625</v>
       </c>
-      <c r="G41" s="22" t="n">
+      <c r="G41" s="38" t="n">
         <f aca="false">$D$28</f>
         <v>0.25</v>
       </c>
@@ -7828,11 +7845,11 @@
         <f aca="false">(B16+B18)*(C16+C18)*(D16+D18)*(E24-(E16+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F42" s="24" t="n">
+      <c r="F42" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C42/PRODUCT($B$24:$F$24))*38+(D42/PRODUCT($B$24:$F$24))*10+(E42/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1015625</v>
       </c>
-      <c r="G42" s="22" t="n">
+      <c r="G42" s="38" t="n">
         <f aca="false">$D$28</f>
         <v>0.25</v>
       </c>
@@ -7856,11 +7873,11 @@
         <f aca="false">(B17+B18)*(C17+C18)*(D17+D18)*(E24-(E17+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F43" s="24" t="n">
+      <c r="F43" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C43/PRODUCT($B$24:$F$24))*25+(D43/PRODUCT($B$24:$F$24))*8+(E43/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.0830078125</v>
       </c>
-      <c r="G43" s="22" t="n">
+      <c r="G43" s="38" t="n">
         <f aca="false">$D$28</f>
         <v>0.25</v>
       </c>
@@ -7884,11 +7901,11 @@
         <f aca="false">(B14+B18+B19)*(C14+C18+C19)*(D14+D18+D19)*(E24-(E14+E18+E19))*$B$24</f>
         <v>384000000</v>
       </c>
-      <c r="F44" s="24" t="n">
+      <c r="F44" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C44/PRODUCT($B$24:$F$24))*100+(D44/PRODUCT($B$24:$F$24))*25+(E44/PRODUCT($B$24:$F$24))*5)</f>
         <v>1.6</v>
       </c>
-      <c r="G44" s="22" t="n">
+      <c r="G44" s="38" t="n">
         <f aca="false">$E$28</f>
         <v>0.25</v>
       </c>
@@ -7912,11 +7929,11 @@
         <f aca="false">(B15+B18)*(C15+C18)*(D15+D18)*(E24-(E15+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F45" s="24" t="n">
+      <c r="F45" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C45/PRODUCT($B$24:$F$24))*50+(D45/PRODUCT($B$24:$F$24))*13+(E45/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1220703125</v>
       </c>
-      <c r="G45" s="22" t="n">
+      <c r="G45" s="38" t="n">
         <f aca="false">$E$28</f>
         <v>0.25</v>
       </c>
@@ -7940,11 +7957,11 @@
         <f aca="false">(B16+B18)*(C16+C18)*(D16+D18)*(E24-(E16+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F46" s="24" t="n">
+      <c r="F46" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C46/PRODUCT($B$24:$F$24))*38+(D46/PRODUCT($B$24:$F$24))*10+(E46/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.1015625</v>
       </c>
-      <c r="G46" s="22" t="n">
+      <c r="G46" s="38" t="n">
         <f aca="false">$E$28</f>
         <v>0.25</v>
       </c>
@@ -7968,11 +7985,11 @@
         <f aca="false">(B17+B18)*(C17+C18)*(D17+D18)*(E24-(E17+E18))*$B$24</f>
         <v>117187500</v>
       </c>
-      <c r="F47" s="24" t="n">
+      <c r="F47" s="39" t="n">
         <f aca="false">IF(PRODUCT($B$24:$F$24)&lt;=0,0,(C47/PRODUCT($B$24:$F$24))*25+(D47/PRODUCT($B$24:$F$24))*8+(E47/PRODUCT($B$24:$F$24))*3)</f>
         <v>0.0830078125</v>
       </c>
-      <c r="G47" s="22" t="n">
+      <c r="G47" s="38" t="n">
         <f aca="false">$E$28</f>
         <v>0.25</v>
       </c>
@@ -8014,23 +8031,23 @@
       <c r="A51" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="B51" s="24" t="n">
+      <c r="B51" s="39" t="n">
         <f aca="false">F32</f>
         <v>0.0326953125</v>
       </c>
-      <c r="C51" s="24" t="n">
+      <c r="C51" s="39" t="n">
         <f aca="false">F36</f>
         <v>0.0326953125</v>
       </c>
-      <c r="D51" s="24" t="n">
+      <c r="D51" s="39" t="n">
         <f aca="false">F40</f>
         <v>0.0326953125</v>
       </c>
-      <c r="E51" s="24" t="n">
+      <c r="E51" s="39" t="n">
         <f aca="false">F44</f>
         <v>1.6</v>
       </c>
-      <c r="F51" s="24" t="n">
+      <c r="F51" s="39" t="n">
         <f aca="false">B51*$B$28+C51*$C$28+D51*$D$28+E51*$E$28</f>
         <v>0.424521484375</v>
       </c>
@@ -8040,23 +8057,23 @@
       <c r="A52" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="24" t="n">
+      <c r="B52" s="39" t="n">
         <f aca="false">F33</f>
         <v>0.1220703125</v>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="39" t="n">
         <f aca="false">F37</f>
         <v>0.1220703125</v>
       </c>
-      <c r="D52" s="24" t="n">
+      <c r="D52" s="39" t="n">
         <f aca="false">F41</f>
         <v>2.15625</v>
       </c>
-      <c r="E52" s="24" t="n">
+      <c r="E52" s="39" t="n">
         <f aca="false">F45</f>
         <v>0.1220703125</v>
       </c>
-      <c r="F52" s="24" t="n">
+      <c r="F52" s="39" t="n">
         <f aca="false">B52*$B$28+C52*$C$28+D52*$D$28+E52*$E$28</f>
         <v>0.630615234375</v>
       </c>
@@ -8066,23 +8083,23 @@
       <c r="A53" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="B53" s="24" t="n">
+      <c r="B53" s="39" t="n">
         <f aca="false">F34</f>
         <v>0.1015625</v>
       </c>
-      <c r="C53" s="24" t="n">
+      <c r="C53" s="39" t="n">
         <f aca="false">F38</f>
         <v>1.6875</v>
       </c>
-      <c r="D53" s="24" t="n">
+      <c r="D53" s="39" t="n">
         <f aca="false">F42</f>
         <v>0.1015625</v>
       </c>
-      <c r="E53" s="24" t="n">
+      <c r="E53" s="39" t="n">
         <f aca="false">F46</f>
         <v>0.1015625</v>
       </c>
-      <c r="F53" s="24" t="n">
+      <c r="F53" s="39" t="n">
         <f aca="false">B53*$B$28+C53*$C$28+D53*$D$28+E53*$E$28</f>
         <v>0.498046875</v>
       </c>
@@ -8092,23 +8109,23 @@
       <c r="A54" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="B54" s="24" t="n">
+      <c r="B54" s="39" t="n">
         <f aca="false">F35</f>
         <v>1.21875</v>
       </c>
-      <c r="C54" s="24" t="n">
+      <c r="C54" s="39" t="n">
         <f aca="false">F39</f>
         <v>0.0830078125</v>
       </c>
-      <c r="D54" s="24" t="n">
+      <c r="D54" s="39" t="n">
         <f aca="false">F43</f>
         <v>0.0830078125</v>
       </c>
-      <c r="E54" s="24" t="n">
+      <c r="E54" s="39" t="n">
         <f aca="false">F47</f>
         <v>0.0830078125</v>
       </c>
-      <c r="F54" s="24" t="n">
+      <c r="F54" s="39" t="n">
         <f aca="false">B54*$B$28+C54*$C$28+D54*$D$28+E54*$E$28</f>
         <v>0.366943359375</v>
       </c>
@@ -8122,7 +8139,7 @@
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
       <c r="E55" s="17"/>
-      <c r="F55" s="25" t="n">
+      <c r="F55" s="40" t="n">
         <f aca="false">SUM(F51:F54)</f>
         <v>1.920126953125</v>
       </c>
